--- a/output/pdf_financials_xlsx/NINE.xlsx
+++ b/output/pdf_financials_xlsx/NINE.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.889849</v>
+        <v>2.70612</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.587416</v>
+        <v>2.216476</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.389434</v>
+        <v>0.903119</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.889849</v>
+        <v>-2.70612</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.587416</v>
+        <v>-2.216476</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.389434</v>
+        <v>-0.903119</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.021026</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.02133</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001209</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.695611</v>
+        <v>-2.716637</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.174887</v>
+        <v>-2.196217</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.883447</v>
+        <v>-0.884656</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.695611</v>
+        <v>-2.716637</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.174887</v>
+        <v>-2.196217</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.883447</v>
+        <v>-0.884656</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.446001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.387469</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.044136</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.446001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.387469</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.044136</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.501323</v>
+        <v>0.055322</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.417506</v>
+        <v>0.030037</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.112067</v>
+        <v>0.06793100000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2428,10 +2428,10 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003285</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008213</v>
       </c>
     </row>
     <row r="125">
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003285</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008213</v>
       </c>
     </row>
     <row r="126">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
@@ -4527,7 +4527,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -5839,7 +5843,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -5961,7 +5965,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5994,7 +5998,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -6457,7 +6461,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
